--- a/Xiaomi电视产品价格表2025-2026.xlsx
+++ b/Xiaomi电视产品价格表2025-2026.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="21600" windowHeight="9555"/>
+    <workbookView windowWidth="21000" windowHeight="8955"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="110">
   <si>
     <t>ASIN</t>
   </si>
@@ -333,6 +333,30 @@
   </si>
   <si>
     <t>G25I 2026</t>
+  </si>
+  <si>
+    <t>B0H26RB46K</t>
+  </si>
+  <si>
+    <t>FX Mini LED-43</t>
+  </si>
+  <si>
+    <t>B0H26SBKX4</t>
+  </si>
+  <si>
+    <t>FX Mini LED-55</t>
+  </si>
+  <si>
+    <t>B0H26TKHL5</t>
+  </si>
+  <si>
+    <t>FX Mini LED-65</t>
+  </si>
+  <si>
+    <t>B0H26V48FQ</t>
+  </si>
+  <si>
+    <t>FX Mini LED-75</t>
   </si>
 </sst>
 </file>
@@ -1019,7 +1043,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1049,16 +1073,10 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1586,7 +1604,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I53"/>
+  <dimension ref="A1:I57"/>
   <sheetFormatPr defaultColWidth="9.02654867256637" defaultRowHeight="13.5"/>
   <cols>
     <col min="4" max="4" width="28.0176991150442" style="1" customWidth="1"/>
@@ -2038,7 +2056,7 @@
         <v>76</v>
       </c>
       <c r="C41" s="10"/>
-      <c r="D41" s="11" t="s">
+      <c r="D41" s="8" t="s">
         <v>77</v>
       </c>
       <c r="E41" s="8"/>
@@ -2051,7 +2069,7 @@
         <v>78</v>
       </c>
       <c r="C42" s="10"/>
-      <c r="D42" s="11" t="s">
+      <c r="D42" s="8" t="s">
         <v>79</v>
       </c>
       <c r="E42" s="8"/>
@@ -2064,7 +2082,7 @@
         <v>80</v>
       </c>
       <c r="C43" s="10"/>
-      <c r="D43" s="11" t="s">
+      <c r="D43" s="8" t="s">
         <v>81</v>
       </c>
       <c r="E43" s="8"/>
@@ -2076,8 +2094,8 @@
       <c r="B44" s="8" t="s">
         <v>82</v>
       </c>
-      <c r="C44" s="12"/>
-      <c r="D44" s="11" t="s">
+      <c r="C44" s="11"/>
+      <c r="D44" s="8" t="s">
         <v>83</v>
       </c>
       <c r="E44" s="8"/>
@@ -2089,8 +2107,8 @@
       <c r="B45" t="s">
         <v>84</v>
       </c>
-      <c r="C45" s="12"/>
-      <c r="D45" s="11" t="s">
+      <c r="C45" s="11"/>
+      <c r="D45" s="8" t="s">
         <v>85</v>
       </c>
       <c r="E45" s="8"/>
@@ -2100,8 +2118,8 @@
       <c r="B46" t="s">
         <v>86</v>
       </c>
-      <c r="C46" s="12"/>
-      <c r="D46" s="11" t="s">
+      <c r="C46" s="11"/>
+      <c r="D46" s="8" t="s">
         <v>87</v>
       </c>
       <c r="E46" s="8"/>
@@ -2111,8 +2129,8 @@
       <c r="B47" t="s">
         <v>88</v>
       </c>
-      <c r="C47" s="12"/>
-      <c r="D47" s="13" t="s">
+      <c r="C47" s="11"/>
+      <c r="D47" s="12" t="s">
         <v>89</v>
       </c>
       <c r="E47" s="8"/>
@@ -2123,7 +2141,7 @@
         <v>90</v>
       </c>
       <c r="C48" s="10"/>
-      <c r="D48" s="11" t="s">
+      <c r="D48" s="8" t="s">
         <v>91</v>
       </c>
       <c r="E48" s="8"/>
@@ -2134,7 +2152,7 @@
         <v>92</v>
       </c>
       <c r="C49" s="10"/>
-      <c r="D49" s="14" t="s">
+      <c r="D49" s="7" t="s">
         <v>93</v>
       </c>
       <c r="E49" s="8"/>
@@ -2145,7 +2163,7 @@
         <v>94</v>
       </c>
       <c r="C50" s="10"/>
-      <c r="D50" s="14" t="s">
+      <c r="D50" s="7" t="s">
         <v>95</v>
       </c>
       <c r="E50" s="8"/>
@@ -2156,7 +2174,7 @@
         <v>96</v>
       </c>
       <c r="C51" s="10"/>
-      <c r="D51" s="14" t="s">
+      <c r="D51" s="7" t="s">
         <v>97</v>
       </c>
       <c r="E51" s="8"/>
@@ -2167,7 +2185,7 @@
         <v>98</v>
       </c>
       <c r="C52" s="10"/>
-      <c r="D52" s="14" t="s">
+      <c r="D52" s="7" t="s">
         <v>99</v>
       </c>
       <c r="E52" s="8"/>
@@ -2178,10 +2196,42 @@
         <v>100</v>
       </c>
       <c r="C53" s="10"/>
-      <c r="D53" s="14" t="s">
+      <c r="D53" s="7" t="s">
         <v>101</v>
       </c>
       <c r="E53" s="8"/>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="B54" t="s">
+        <v>102</v>
+      </c>
+      <c r="D54" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="B55" t="s">
+        <v>104</v>
+      </c>
+      <c r="D55" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="B56" t="s">
+        <v>106</v>
+      </c>
+      <c r="D56" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="B57" t="s">
+        <v>108</v>
+      </c>
+      <c r="D57" t="s">
+        <v>109</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
